--- a/ig/DM-OCTOBRE-2026/ValueSet-vs-tre-r430-modalite-reconnaissance-contractuelle.xlsx
+++ b/ig/DM-OCTOBRE-2026/ValueSet-vs-tre-r430-modalite-reconnaissance-contractuelle.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Vs Tre R430 Modalité Reconnaissance Contractuelle</t>
+    <t>Vs Tre R430 Modalite Reconnaissance Contractuelle</t>
   </si>
   <si>
     <t>Status</t>
